--- a/results/qwen25vl3b_7b_answer_grpo_selected25_temp06_3seed_mean_std.xlsx
+++ b/results/qwen25vl3b_7b_answer_grpo_selected25_temp06_3seed_mean_std.xlsx
@@ -972,40 +972,40 @@
         <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>19.8</v>
+        <v>34.09</v>
       </c>
       <c r="D12" t="n">
-        <v>0.76</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>21.4</v>
+        <v>39.59</v>
       </c>
       <c r="F12" t="n">
-        <v>1.02</v>
+        <v>1.37</v>
       </c>
       <c r="G12" t="n">
-        <v>1.61</v>
+        <v>5.5</v>
       </c>
       <c r="H12" t="n">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="I12" t="n">
-        <v>23.9</v>
+        <v>43.82</v>
       </c>
       <c r="J12" t="n">
-        <v>1.23</v>
+        <v>0.29</v>
       </c>
       <c r="K12" t="n">
-        <v>24.87</v>
+        <v>46.4</v>
       </c>
       <c r="L12" t="n">
-        <v>0.13</v>
+        <v>1.11</v>
       </c>
       <c r="M12" t="n">
-        <v>0.97</v>
+        <v>2.58</v>
       </c>
       <c r="N12" t="n">
-        <v>1.36</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="13">
@@ -1662,40 +1662,40 @@
         <v>3</v>
       </c>
       <c r="C27" t="n">
-        <v>35.88</v>
+        <v>36.46</v>
       </c>
       <c r="D27" t="n">
         <v>0.52</v>
       </c>
       <c r="E27" t="n">
-        <v>39.1</v>
+        <v>39.83</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="G27" t="n">
-        <v>3.21</v>
+        <v>3.37</v>
       </c>
       <c r="H27" t="n">
         <v>0.32</v>
       </c>
       <c r="I27" t="n">
-        <v>43.67</v>
+        <v>44.47</v>
       </c>
       <c r="J27" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="K27" t="n">
-        <v>47.51</v>
+        <v>48.37</v>
       </c>
       <c r="L27" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="M27" t="n">
-        <v>3.84</v>
+        <v>3.9</v>
       </c>
       <c r="N27" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -2604,22 +2604,22 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>19.0355</v>
+        <v>34.1371</v>
       </c>
       <c r="D32" t="n">
-        <v>21.3198</v>
+        <v>38.0711</v>
       </c>
       <c r="E32" t="n">
-        <v>25.2538</v>
+        <v>43.6548</v>
       </c>
       <c r="F32" t="n">
-        <v>24.7462</v>
+        <v>45.1777</v>
       </c>
       <c r="G32" t="n">
-        <v>2.2843</v>
+        <v>3.934</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.5076000000000001</v>
+        <v>1.5229</v>
       </c>
     </row>
     <row r="33">
@@ -2632,22 +2632,22 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>19.797</v>
+        <v>34.1371</v>
       </c>
       <c r="D33" t="n">
-        <v>22.4619</v>
+        <v>40.736</v>
       </c>
       <c r="E33" t="n">
-        <v>23.6041</v>
+        <v>43.6548</v>
       </c>
       <c r="F33" t="n">
-        <v>24.8731</v>
+        <v>46.7005</v>
       </c>
       <c r="G33" t="n">
-        <v>2.665</v>
+        <v>6.5989</v>
       </c>
       <c r="H33" t="n">
-        <v>1.269</v>
+        <v>3.0457</v>
       </c>
     </row>
     <row r="34">
@@ -2660,22 +2660,22 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>20.5584</v>
+        <v>34.0102</v>
       </c>
       <c r="D34" t="n">
-        <v>20.4315</v>
+        <v>39.9746</v>
       </c>
       <c r="E34" t="n">
-        <v>22.8426</v>
+        <v>44.1624</v>
       </c>
       <c r="F34" t="n">
-        <v>25</v>
+        <v>47.335</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.1269</v>
+        <v>5.9644</v>
       </c>
       <c r="H34" t="n">
-        <v>2.1574</v>
+        <v>3.1726</v>
       </c>
     </row>
     <row r="35">
@@ -3864,22 +3864,22 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>35.5613</v>
+        <v>36.1654</v>
       </c>
       <c r="D77" t="n">
-        <v>38.9967</v>
+        <v>39.6668</v>
       </c>
       <c r="E77" t="n">
-        <v>43.7163</v>
+        <v>44.4523</v>
       </c>
       <c r="F77" t="n">
-        <v>47.4016</v>
+        <v>48.2189</v>
       </c>
       <c r="G77" t="n">
-        <v>3.4354</v>
+        <v>3.5014</v>
       </c>
       <c r="H77" t="n">
-        <v>3.6853</v>
+        <v>3.7665</v>
       </c>
     </row>
     <row r="78">
@@ -3892,22 +3892,22 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>36.4822</v>
+        <v>37.0558</v>
       </c>
       <c r="D78" t="n">
-        <v>39.3346</v>
+        <v>40.0655</v>
       </c>
       <c r="E78" t="n">
-        <v>43.9391</v>
+        <v>44.7412</v>
       </c>
       <c r="F78" t="n">
-        <v>47.6184</v>
+        <v>48.4915</v>
       </c>
       <c r="G78" t="n">
-        <v>2.8524</v>
+        <v>3.0097</v>
       </c>
       <c r="H78" t="n">
-        <v>3.6792</v>
+        <v>3.7503</v>
       </c>
     </row>
     <row r="79">
@@ -3920,22 +3920,22 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>35.6099</v>
+        <v>36.148</v>
       </c>
       <c r="D79" t="n">
-        <v>38.9657</v>
+        <v>39.7474</v>
       </c>
       <c r="E79" t="n">
-        <v>43.3548</v>
+        <v>44.2076</v>
       </c>
       <c r="F79" t="n">
-        <v>47.5007</v>
+        <v>48.3941</v>
       </c>
       <c r="G79" t="n">
-        <v>3.3558</v>
+        <v>3.5994</v>
       </c>
       <c r="H79" t="n">
-        <v>4.1459</v>
+        <v>4.1865</v>
       </c>
     </row>
   </sheetData>
@@ -3949,7 +3949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4071,6 +4071,23 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>mathverse_fix</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Corrected MathVerse local judge parser to accept outputs like "Judgement: 1" from Qwen3-32B.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Updated MathVerse row from existing judged artifacts; no generation rerun.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/qwen25vl3b_7b_answer_grpo_selected25_temp06_3seed_mean_std.xlsx
+++ b/results/qwen25vl3b_7b_answer_grpo_selected25_temp06_3seed_mean_std.xlsx
@@ -1340,40 +1340,40 @@
         <v>3</v>
       </c>
       <c r="C20" t="n">
-        <v>60.51</v>
+        <v>68.19</v>
       </c>
       <c r="D20" t="n">
-        <v>9.24</v>
+        <v>3.08</v>
       </c>
       <c r="E20" t="n">
-        <v>58.75</v>
+        <v>64.02</v>
       </c>
       <c r="F20" t="n">
-        <v>7.07</v>
+        <v>6.45</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.76</v>
+        <v>-4.17</v>
       </c>
       <c r="H20" t="n">
-        <v>6.81</v>
+        <v>5.99</v>
       </c>
       <c r="I20" t="n">
-        <v>72.8</v>
+        <v>72.64</v>
       </c>
       <c r="J20" t="n">
-        <v>4.49</v>
+        <v>4.6</v>
       </c>
       <c r="K20" t="n">
-        <v>77.73</v>
+        <v>77.86</v>
       </c>
       <c r="L20" t="n">
-        <v>0.33</v>
+        <v>0.61</v>
       </c>
       <c r="M20" t="n">
-        <v>4.93</v>
+        <v>5.21</v>
       </c>
       <c r="N20" t="n">
-        <v>4.6</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="21">
@@ -1658,45 +1658,31 @@
           <t>Average</t>
         </is>
       </c>
-      <c r="B27" t="n">
-        <v>3</v>
-      </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>36.46</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.52</v>
-      </c>
+        <v>36.76</v>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
-        <v>39.83</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.21</v>
-      </c>
+        <v>40.04</v>
+      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.32</v>
-      </c>
+        <v>3.27</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>44.47</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.27</v>
-      </c>
+        <v>44.46</v>
+      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="n">
         <v>48.37</v>
       </c>
-      <c r="L27" t="n">
-        <v>0.14</v>
-      </c>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0.25</v>
-      </c>
+        <v>3.91</v>
+      </c>
+      <c r="N27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3276,22 +3262,22 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>50</v>
+        <v>64.9371</v>
       </c>
       <c r="D56" t="n">
-        <v>54.3239</v>
+        <v>64.2296</v>
       </c>
       <c r="E56" t="n">
-        <v>77.12260000000001</v>
+        <v>77.2013</v>
       </c>
       <c r="F56" t="n">
-        <v>77.8302</v>
+        <v>77.673</v>
       </c>
       <c r="G56" t="n">
-        <v>4.3239</v>
+        <v>-0.707499999999996</v>
       </c>
       <c r="H56" t="n">
-        <v>0.7076</v>
+        <v>0.4716999999999985</v>
       </c>
     </row>
     <row r="57">
@@ -3304,22 +3290,22 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>64.15089999999999</v>
+        <v>68.5535</v>
       </c>
       <c r="D57" t="n">
-        <v>55.0314</v>
+        <v>57.4686</v>
       </c>
       <c r="E57" t="n">
-        <v>68.1604</v>
+        <v>68.0031</v>
       </c>
       <c r="F57" t="n">
-        <v>77.98739999999999</v>
+        <v>78.5377</v>
       </c>
       <c r="G57" t="n">
-        <v>-9.1195</v>
+        <v>-11.0849</v>
       </c>
       <c r="H57" t="n">
-        <v>9.827</v>
+        <v>10.5346</v>
       </c>
     </row>
     <row r="58">
@@ -3332,22 +3318,22 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>67.3742</v>
+        <v>71.0692</v>
       </c>
       <c r="D58" t="n">
-        <v>66.9025</v>
+        <v>70.3616</v>
       </c>
       <c r="E58" t="n">
-        <v>73.11320000000001</v>
+        <v>72.7201</v>
       </c>
       <c r="F58" t="n">
         <v>77.35850000000001</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.4717</v>
+        <v>-0.7075999999999993</v>
       </c>
       <c r="H58" t="n">
-        <v>4.2453</v>
+        <v>4.638400000000004</v>
       </c>
     </row>
     <row r="59">
@@ -3456,10 +3442,10 @@
         <v>78.13330000000001</v>
       </c>
       <c r="G62" t="n">
-        <v>2.8534</v>
+        <v>2.853400000000008</v>
       </c>
       <c r="H62" t="n">
-        <v>4.5066</v>
+        <v>4.506600000000006</v>
       </c>
     </row>
     <row r="63">
@@ -3484,10 +3470,10 @@
         <v>77.44</v>
       </c>
       <c r="G63" t="n">
-        <v>2.56</v>
+        <v>2.560000000000002</v>
       </c>
       <c r="H63" t="n">
-        <v>2.0533</v>
+        <v>2.053299999999993</v>
       </c>
     </row>
     <row r="64">
@@ -3512,10 +3498,10 @@
         <v>78.40000000000001</v>
       </c>
       <c r="G64" t="n">
-        <v>2.88</v>
+        <v>2.879999999999995</v>
       </c>
       <c r="H64" t="n">
-        <v>2.6667</v>
+        <v>2.666700000000006</v>
       </c>
     </row>
     <row r="65">
@@ -3949,7 +3935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4088,6 +4074,23 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>screenspot_table_repair</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ScreenSpot positional clicks and TableVQABench final-answer wrappers re-parsed from cached predictions.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>No generation or judge rerun.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/qwen25vl3b_7b_answer_grpo_selected25_temp06_3seed_mean_std.xlsx
+++ b/results/qwen25vl3b_7b_answer_grpo_selected25_temp06_3seed_mean_std.xlsx
@@ -1524,40 +1524,40 @@
         <v>3</v>
       </c>
       <c r="C24" t="n">
-        <v>17.32</v>
+        <v>18.49</v>
       </c>
       <c r="D24" t="n">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="E24" t="n">
-        <v>18.86</v>
+        <v>21.03</v>
       </c>
       <c r="F24" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="G24" t="n">
-        <v>1.54</v>
+        <v>2.54</v>
       </c>
       <c r="H24" t="n">
-        <v>0.82</v>
+        <v>0.99</v>
       </c>
       <c r="I24" t="n">
-        <v>19.35</v>
+        <v>21.66</v>
       </c>
       <c r="J24" t="n">
-        <v>1.64</v>
+        <v>2.18</v>
       </c>
       <c r="K24" t="n">
-        <v>22.32</v>
+        <v>24.49</v>
       </c>
       <c r="L24" t="n">
-        <v>2.06</v>
+        <v>2.27</v>
       </c>
       <c r="M24" t="n">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="N24" t="n">
-        <v>0.57</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="25">
@@ -1660,23 +1660,23 @@
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>36.76</v>
+        <v>36.81</v>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
-        <v>40.04</v>
+        <v>40.12</v>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="n">
-        <v>3.27</v>
+        <v>3.31</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>44.46</v>
+        <v>44.55</v>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="n">
-        <v>48.37</v>
+        <v>48.46</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="n">
@@ -3598,22 +3598,22 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>16.0959</v>
+        <v>17.12328767123288</v>
       </c>
       <c r="D68" t="n">
-        <v>18.5788</v>
+        <v>20.80479452054794</v>
       </c>
       <c r="E68" t="n">
-        <v>18.2363</v>
+        <v>20.03424657534246</v>
       </c>
       <c r="F68" t="n">
-        <v>20.5479</v>
+        <v>22.77397260273973</v>
       </c>
       <c r="G68" t="n">
-        <v>2.4829</v>
+        <v>3.681506849315067</v>
       </c>
       <c r="H68" t="n">
-        <v>2.3116</v>
+        <v>2.739726027397261</v>
       </c>
     </row>
     <row r="69">
@@ -3626,22 +3626,22 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>17.9795</v>
+        <v>19.17808219178082</v>
       </c>
       <c r="D69" t="n">
-        <v>19.0068</v>
+        <v>21.23287671232877</v>
       </c>
       <c r="E69" t="n">
-        <v>21.2329</v>
+        <v>24.14383561643836</v>
       </c>
       <c r="F69" t="n">
-        <v>24.5719</v>
+        <v>27.05479452054795</v>
       </c>
       <c r="G69" t="n">
-        <v>1.0274</v>
+        <v>2.054794520547947</v>
       </c>
       <c r="H69" t="n">
-        <v>3.339</v>
+        <v>2.910958904109592</v>
       </c>
     </row>
     <row r="70">
@@ -3654,22 +3654,22 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>17.8938</v>
+        <v>19.17808219178082</v>
       </c>
       <c r="D70" t="n">
-        <v>19.0068</v>
+        <v>21.06164383561644</v>
       </c>
       <c r="E70" t="n">
-        <v>18.5788</v>
+        <v>20.80479452054794</v>
       </c>
       <c r="F70" t="n">
-        <v>21.8322</v>
+        <v>23.63013698630137</v>
       </c>
       <c r="G70" t="n">
-        <v>1.113</v>
+        <v>1.88356164383562</v>
       </c>
       <c r="H70" t="n">
-        <v>3.2534</v>
+        <v>2.825342465753426</v>
       </c>
     </row>
     <row r="71">
@@ -3935,7 +3935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4091,6 +4091,23 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>visualpuzzles_repair</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Re-scored cached Qwen3 extraction outputs with VisualPuzzles A-D option contract.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>No generation or judge rerun.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/qwen25vl3b_7b_answer_grpo_selected25_temp06_3seed_mean_std.xlsx
+++ b/results/qwen25vl3b_7b_answer_grpo_selected25_temp06_3seed_mean_std.xlsx
@@ -2602,7 +2602,7 @@
         <v>45.1777</v>
       </c>
       <c r="G32" t="n">
-        <v>3.934</v>
+        <v>3.934000000000005</v>
       </c>
       <c r="H32" t="n">
         <v>1.5229</v>
@@ -2633,7 +2633,7 @@
         <v>6.5989</v>
       </c>
       <c r="H33" t="n">
-        <v>3.0457</v>
+        <v>3.045699999999997</v>
       </c>
     </row>
     <row r="34">
@@ -2658,10 +2658,10 @@
         <v>47.335</v>
       </c>
       <c r="G34" t="n">
-        <v>5.9644</v>
+        <v>5.964400000000005</v>
       </c>
       <c r="H34" t="n">
-        <v>3.1726</v>
+        <v>3.172600000000003</v>
       </c>
     </row>
     <row r="35">
@@ -3935,7 +3935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4108,6 +4108,23 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>mathverse_judgement_repair</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>MathVerse local Qwen3-32B judge outputs of the form `Judgement: 1` are counted as correct.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>No generation or judge rerun.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
